--- a/data/base/Backlog_29.xlsx
+++ b/data/base/Backlog_29.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1264275A-5F5F-4069-B4FA-C03A7D199F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCC4C4A-211C-4A04-B3BB-3E66BD6277FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{C661A4F2-BBF1-4093-B8A4-9B6A289CC3D5}"/>
+    <workbookView xWindow="-24525" yWindow="555" windowWidth="21600" windowHeight="11295" xr2:uid="{C661A4F2-BBF1-4093-B8A4-9B6A289CC3D5}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="1" r:id="rId1"/>
